--- a/daisu/sample_data/가상구시설관리공단_교육자료/01_인사/2026_직원현황(10월1일자).xlsx
+++ b/daisu/sample_data/가상구시설관리공단_교육자료/01_인사/2026_직원현황(10월1일자).xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,45 +454,55 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>직급</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>고용형태</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>직무구분</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>근무형태</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>근무조</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>입사일</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>승진일</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>퇴사일</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>휴직기간</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>개인정보취급자</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>관리감독자</t>
         </is>
@@ -521,31 +531,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>3급</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" s="2" t="n">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>39815</v>
       </c>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,31 +586,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" s="2" t="n">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>42187</v>
       </c>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -619,27 +641,33 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" s="2" t="n">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
         <v>40469</v>
       </c>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -664,31 +692,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" s="2" t="n">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
         <v>45719</v>
       </c>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -713,31 +747,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" s="2" t="n">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
         <v>40321</v>
       </c>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -762,27 +802,33 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" s="2" t="n">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
         <v>44832</v>
       </c>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -807,31 +853,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" s="2" t="n">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
         <v>39823</v>
       </c>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -856,31 +908,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" s="2" t="n">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" s="2" t="n">
         <v>45365</v>
       </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -905,27 +963,33 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" s="2" t="n">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
         <v>42980</v>
       </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -950,33 +1014,39 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>7급</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" s="2" t="n">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
         <v>40279</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1001,31 +1071,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" s="2" t="n">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
         <v>43663</v>
       </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1050,27 +1126,33 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>기간제</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" s="2" t="n">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" s="2" t="n">
         <v>41453</v>
       </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1095,31 +1177,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>3급</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" s="2" t="n">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="2" t="n">
         <v>45165</v>
       </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1144,31 +1232,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" s="2" t="n">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1193,27 +1287,33 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" s="2" t="n">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" s="2" t="n">
         <v>43167</v>
       </c>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1238,31 +1338,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" s="2" t="n">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1287,31 +1393,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" s="2" t="n">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
         <v>39679</v>
       </c>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1336,27 +1448,33 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" s="2" t="n">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
         <v>39873</v>
       </c>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1381,31 +1499,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" s="2" t="n">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1430,31 +1554,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>7급</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" s="2" t="n">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" s="2" t="n">
         <v>41630</v>
       </c>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1479,27 +1609,33 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>3급</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" s="2" t="n">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" s="2" t="n">
         <v>45482</v>
       </c>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1528,27 +1664,35 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>4급</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" s="2" t="n">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" s="2" t="n">
         <v>41163</v>
       </c>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+      <c r="K25" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1577,27 +1721,33 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>4급</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" s="2" t="n">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" s="2" t="n">
         <v>41658</v>
       </c>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1626,31 +1776,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" s="2" t="n">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
         <v>41444</v>
       </c>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1675,31 +1831,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" s="2" t="n">
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" s="2" t="n">
         <v>43283</v>
       </c>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1724,31 +1886,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" s="2" t="n">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" s="2" t="n">
         <v>44283</v>
       </c>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1773,31 +1941,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="J30" s="2" t="n">
         <v>40799</v>
       </c>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1822,31 +1996,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="J31" s="2" t="n">
         <v>40582</v>
       </c>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1871,31 +2051,37 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="J32" s="2" t="n">
         <v>40456</v>
       </c>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1920,31 +2106,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="J33" s="2" t="n">
         <v>44943</v>
       </c>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1969,31 +2161,37 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="J34" s="2" t="n">
         <v>39613</v>
       </c>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2018,31 +2216,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="J35" s="2" t="n">
         <v>45527</v>
       </c>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2067,31 +2271,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="J36" s="2" t="n">
         <v>43378</v>
       </c>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
       <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2116,31 +2326,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="J37" s="2" t="n">
         <v>43534</v>
       </c>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
       <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2165,31 +2381,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="J38" s="2" t="n">
         <v>40441</v>
       </c>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
       <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2214,31 +2436,37 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="J39" s="2" t="n">
         <v>43520</v>
       </c>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
       <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2263,31 +2491,39 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="J40" s="2" t="n">
         <v>41330</v>
       </c>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="K40" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L40" s="2" t="n"/>
       <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2312,31 +2548,37 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
+      <c r="J41" s="2" t="n">
         <v>45728</v>
       </c>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
       <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2361,31 +2603,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="J42" s="2" t="n">
         <v>45643</v>
       </c>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
       <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2410,31 +2658,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="J43" s="2" t="n">
         <v>40478</v>
       </c>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
       <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2459,31 +2713,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="J44" s="2" t="n">
         <v>44069</v>
       </c>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
       <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2508,31 +2768,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="J45" s="2" t="n">
         <v>44362</v>
       </c>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
       <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2557,31 +2823,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="J46" s="2" t="n">
         <v>45217</v>
       </c>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
       <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2606,31 +2878,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>7급</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="J47" s="2" t="n">
         <v>43176</v>
       </c>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
       <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2655,31 +2933,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="J48" s="2" t="n">
         <v>42062</v>
       </c>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
       <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2704,31 +2988,37 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
+      <c r="J49" s="2" t="n">
         <v>44169</v>
       </c>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
       <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2753,31 +3043,37 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>7급</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="J50" s="2" t="n">
         <v>43171</v>
       </c>
-      <c r="J50" s="2" t="n"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
       <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2802,31 +3098,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="J51" s="2" t="n">
         <v>39761</v>
       </c>
-      <c r="J51" s="2" t="n"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
       <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2851,31 +3153,37 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="J52" s="2" t="n">
         <v>40316</v>
       </c>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
       <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2900,31 +3208,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="J53" s="2" t="n">
         <v>45538</v>
       </c>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
       <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2949,31 +3263,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G54" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="J54" s="2" t="n">
         <v>40841</v>
       </c>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
       <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2998,31 +3318,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
+      <c r="J55" s="2" t="n">
         <v>40504</v>
       </c>
-      <c r="J55" s="2" t="n"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
       <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3047,31 +3373,37 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="J56" s="2" t="n">
         <v>42172</v>
       </c>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
       <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3096,31 +3428,37 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>기간제</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
+      <c r="J57" s="2" t="n">
         <v>45920</v>
       </c>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
       <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3145,31 +3483,37 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>기간제</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="J58" s="2" t="n">
         <v>45967</v>
       </c>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
       <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3194,31 +3538,39 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>기간제</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="J59" s="2" t="n">
         <v>46266</v>
       </c>
-      <c r="J59" s="2" t="n"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="K59" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L59" s="2" t="n"/>
       <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3243,27 +3595,33 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>3급</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" s="2" t="n">
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" s="2" t="n">
         <v>39922</v>
       </c>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3292,27 +3650,35 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>4급</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" s="2" t="n">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" s="2" t="n">
         <v>42640</v>
       </c>
-      <c r="J61" s="2" t="n"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
+      <c r="K61" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3341,27 +3707,33 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>4급</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" s="2" t="n">
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" s="2" t="n">
         <v>40172</v>
       </c>
-      <c r="J62" s="2" t="n"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="n"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3390,31 +3762,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
+      <c r="J63" s="2" t="n">
         <v>42285</v>
       </c>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
       <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3439,31 +3817,37 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="J64" s="2" t="n">
         <v>44702</v>
       </c>
-      <c r="J64" s="2" t="n"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
       <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3488,31 +3872,37 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
+      <c r="J65" s="2" t="n">
         <v>40291</v>
       </c>
-      <c r="J65" s="2" t="n"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="n"/>
       <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3537,31 +3927,37 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
+      <c r="J66" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="J66" s="2" t="n"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="n"/>
       <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3586,31 +3982,37 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
+      <c r="J67" s="2" t="n">
         <v>42655</v>
       </c>
-      <c r="J67" s="2" t="n"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="n"/>
       <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3635,31 +4037,39 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
+      <c r="J68" s="2" t="n">
         <v>43521</v>
       </c>
-      <c r="J68" s="2" t="n"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="K68" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L68" s="2" t="n"/>
       <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3684,31 +4094,37 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
+      <c r="J69" s="2" t="n">
         <v>43509</v>
       </c>
-      <c r="J69" s="2" t="n"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
       <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3733,31 +4149,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
+      <c r="J70" s="2" t="n">
         <v>40052</v>
       </c>
-      <c r="J70" s="2" t="n"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="2" t="n"/>
       <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3782,31 +4204,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
+      <c r="J71" s="2" t="n">
         <v>42068</v>
       </c>
-      <c r="J71" s="2" t="n"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="n"/>
       <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3831,35 +4259,41 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
+      <c r="J72" s="2" t="n">
         <v>43275</v>
       </c>
-      <c r="J72" s="2" t="n"/>
-      <c r="K72" t="inlineStr">
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" t="inlineStr">
         <is>
           <t>2026.08.01~2026.11.30</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3884,31 +4318,37 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
+      <c r="J73" s="2" t="n">
         <v>39798</v>
       </c>
-      <c r="J73" s="2" t="n"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="n"/>
       <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3933,31 +4373,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
+      <c r="J74" s="2" t="n">
         <v>42478</v>
       </c>
-      <c r="J74" s="2" t="n"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+      <c r="K74" s="2" t="n"/>
+      <c r="L74" s="2" t="n"/>
       <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3982,31 +4428,37 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
+      <c r="J75" s="2" t="n">
         <v>44683</v>
       </c>
-      <c r="J75" s="2" t="n"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="n"/>
       <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4031,31 +4483,37 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
+      <c r="J76" s="2" t="n">
         <v>39958</v>
       </c>
-      <c r="J76" s="2" t="n"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+      <c r="K76" s="2" t="n"/>
+      <c r="L76" s="2" t="n"/>
       <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4080,31 +4538,37 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>7급</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
+      <c r="J77" s="2" t="n">
         <v>45795</v>
       </c>
-      <c r="J77" s="2" t="n"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="K77" s="2" t="n"/>
+      <c r="L77" s="2" t="n"/>
       <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4129,31 +4593,37 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="J78" s="2" t="n">
         <v>42529</v>
       </c>
-      <c r="J78" s="2" t="n"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" s="2" t="n"/>
       <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4178,31 +4648,37 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
+      <c r="J79" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="J79" s="2" t="n"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
+      <c r="K79" s="2" t="n"/>
+      <c r="L79" s="2" t="n"/>
       <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4227,31 +4703,37 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
+      <c r="J80" s="2" t="n">
         <v>43990</v>
       </c>
-      <c r="J80" s="2" t="n"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+      <c r="K80" s="2" t="n"/>
+      <c r="L80" s="2" t="n"/>
       <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4276,31 +4758,37 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G81" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
+      <c r="J81" s="2" t="n">
         <v>40128</v>
       </c>
-      <c r="J81" s="2" t="n"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
+      <c r="K81" s="2" t="n"/>
+      <c r="L81" s="2" t="n"/>
       <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4325,31 +4813,37 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>7급</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>기간제</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="J82" s="2" t="n">
         <v>43855</v>
       </c>
-      <c r="J82" s="2" t="n"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
+      <c r="K82" s="2" t="n"/>
+      <c r="L82" s="2" t="n"/>
       <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4374,31 +4868,37 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>기간제</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
+      <c r="J83" s="2" t="n">
         <v>46266</v>
       </c>
-      <c r="J83" s="2" t="n"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
+      <c r="K83" s="2" t="n"/>
+      <c r="L83" s="2" t="n"/>
       <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4423,27 +4923,33 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>3급</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" s="2" t="n">
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" s="2" t="n">
         <v>44370</v>
       </c>
-      <c r="J84" s="2" t="n"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4472,27 +4978,33 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>4급</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" s="2" t="n">
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" s="2" t="n">
         <v>41510</v>
       </c>
-      <c r="J85" s="2" t="n"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
+      <c r="K85" s="2" t="n"/>
+      <c r="L85" s="2" t="n"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4521,27 +5033,33 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>4급</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" s="2" t="n">
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" s="2" t="n">
         <v>40970</v>
       </c>
-      <c r="J86" s="2" t="n"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
+      <c r="K86" s="2" t="n"/>
+      <c r="L86" s="2" t="n"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4570,27 +5088,33 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" s="2" t="n">
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" s="2" t="n">
         <v>42631</v>
       </c>
-      <c r="J87" s="2" t="n"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
+      <c r="K87" s="2" t="n"/>
+      <c r="L87" s="2" t="n"/>
       <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4615,31 +5139,37 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
+      <c r="J88" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="J88" s="2" t="n"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="2" t="n"/>
       <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4664,31 +5194,37 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
+      <c r="J89" s="2" t="n">
         <v>45994</v>
       </c>
-      <c r="J89" s="2" t="n"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+      <c r="K89" s="2" t="n"/>
+      <c r="L89" s="2" t="n"/>
       <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4713,31 +5249,37 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
+      <c r="J90" s="2" t="n">
         <v>45100</v>
       </c>
-      <c r="J90" s="2" t="n"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+      <c r="K90" s="2" t="n"/>
+      <c r="L90" s="2" t="n"/>
       <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4762,31 +5304,37 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
+      <c r="J91" s="2" t="n">
         <v>41840</v>
       </c>
-      <c r="J91" s="2" t="n"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" s="2" t="n"/>
+      <c r="L91" s="2" t="n"/>
       <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4811,31 +5359,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
+      <c r="J92" s="2" t="n">
         <v>42391</v>
       </c>
-      <c r="J92" s="2" t="n"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
+      <c r="K92" s="2" t="n"/>
+      <c r="L92" s="2" t="n"/>
       <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4860,31 +5414,37 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
+      <c r="J93" s="2" t="n">
         <v>43662</v>
       </c>
-      <c r="J93" s="2" t="n"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+      <c r="K93" s="2" t="n"/>
+      <c r="L93" s="2" t="n"/>
       <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4909,31 +5469,37 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
+      <c r="J94" s="2" t="n">
         <v>42202</v>
       </c>
-      <c r="J94" s="2" t="n"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+      <c r="K94" s="2" t="n"/>
+      <c r="L94" s="2" t="n"/>
       <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4958,31 +5524,37 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
+      <c r="J95" s="2" t="n">
         <v>42022</v>
       </c>
-      <c r="J95" s="2" t="n"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="K95" s="2" t="n"/>
+      <c r="L95" s="2" t="n"/>
       <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5007,31 +5579,37 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
+      <c r="J96" s="2" t="n">
         <v>40426</v>
       </c>
-      <c r="J96" s="2" t="n"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
+      <c r="K96" s="2" t="n"/>
+      <c r="L96" s="2" t="n"/>
       <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5056,31 +5634,37 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
+      <c r="J97" s="2" t="n">
         <v>41038</v>
       </c>
-      <c r="J97" s="2" t="n"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="K97" s="2" t="n"/>
+      <c r="L97" s="2" t="n"/>
       <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5105,31 +5689,37 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G98" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n">
+      <c r="J98" s="2" t="n">
         <v>42425</v>
       </c>
-      <c r="J98" s="2" t="n"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
+      <c r="K98" s="2" t="n"/>
+      <c r="L98" s="2" t="n"/>
       <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5154,31 +5744,37 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G99" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
+      <c r="J99" s="2" t="n">
         <v>44548</v>
       </c>
-      <c r="J99" s="2" t="n"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
+      <c r="K99" s="2" t="n"/>
+      <c r="L99" s="2" t="n"/>
       <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5203,31 +5799,37 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G100" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I100" s="2" t="n">
+      <c r="J100" s="2" t="n">
         <v>45603</v>
       </c>
-      <c r="J100" s="2" t="n"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
+      <c r="K100" s="2" t="n"/>
+      <c r="L100" s="2" t="n"/>
       <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5252,31 +5854,37 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G101" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n">
+      <c r="J101" s="2" t="n">
         <v>40749</v>
       </c>
-      <c r="J101" s="2" t="n"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+      <c r="K101" s="2" t="n"/>
+      <c r="L101" s="2" t="n"/>
       <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5301,31 +5909,37 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>7급</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G102" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I102" s="2" t="n">
+      <c r="J102" s="2" t="n">
         <v>44258</v>
       </c>
-      <c r="J102" s="2" t="n"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
+      <c r="K102" s="2" t="n"/>
+      <c r="L102" s="2" t="n"/>
       <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5350,31 +5964,37 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>7급</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G103" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I103" s="2" t="n">
+      <c r="J103" s="2" t="n">
         <v>42759</v>
       </c>
-      <c r="J103" s="2" t="n"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
+      <c r="K103" s="2" t="n"/>
+      <c r="L103" s="2" t="n"/>
       <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5399,31 +6019,37 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>기간제</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G104" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I104" s="2" t="n">
+      <c r="J104" s="2" t="n">
         <v>42159</v>
       </c>
-      <c r="J104" s="2" t="n"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
+      <c r="K104" s="2" t="n"/>
+      <c r="L104" s="2" t="n"/>
       <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5448,31 +6074,37 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t>기간제</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
       <c r="G105" t="inlineStr">
         <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
           <t>교대</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I105" s="2" t="n">
+      <c r="J105" s="2" t="n">
         <v>46300</v>
       </c>
-      <c r="J105" s="2" t="n"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
+      <c r="K105" s="2" t="n"/>
+      <c r="L105" s="2" t="n"/>
       <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5497,31 +6129,37 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>3급</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" s="2" t="n">
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" s="2" t="n">
         <v>41463</v>
       </c>
-      <c r="J106" s="2" t="n"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr">
+      <c r="K106" s="2" t="n"/>
+      <c r="L106" s="2" t="n"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5546,31 +6184,37 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" s="2" t="n">
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" s="2" t="n">
         <v>40820</v>
       </c>
-      <c r="J107" s="2" t="n"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr">
+      <c r="K107" s="2" t="n"/>
+      <c r="L107" s="2" t="n"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5595,27 +6239,33 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" s="2" t="n">
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" s="2" t="n">
         <v>41664</v>
       </c>
-      <c r="J108" s="2" t="n"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
+      <c r="K108" s="2" t="n"/>
+      <c r="L108" s="2" t="n"/>
       <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5640,31 +6290,37 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" s="2" t="n">
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" s="2" t="n">
         <v>42954</v>
       </c>
-      <c r="J109" s="2" t="n"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr">
+      <c r="K109" s="2" t="n"/>
+      <c r="L109" s="2" t="n"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5689,31 +6345,37 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" s="2" t="n">
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" s="2" t="n">
         <v>42463</v>
       </c>
-      <c r="J110" s="2" t="n"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr">
+      <c r="K110" s="2" t="n"/>
+      <c r="L110" s="2" t="n"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5738,27 +6400,33 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" s="2" t="n">
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" s="2" t="n">
         <v>42700</v>
       </c>
-      <c r="J111" s="2" t="n"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
+      <c r="K111" s="2" t="n"/>
+      <c r="L111" s="2" t="n"/>
       <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5783,35 +6451,41 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" s="2" t="n">
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" s="2" t="n">
         <v>43105</v>
       </c>
-      <c r="J112" s="2" t="n"/>
-      <c r="K112" t="inlineStr">
+      <c r="K112" s="2" t="n"/>
+      <c r="L112" s="2" t="n"/>
+      <c r="M112" t="inlineStr">
         <is>
           <t>2026.03.01~2027.02.28</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="N112" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5836,31 +6510,37 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" s="2" t="n">
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" s="2" t="n">
         <v>43704</v>
       </c>
-      <c r="J113" s="2" t="n"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr">
+      <c r="K113" s="2" t="n"/>
+      <c r="L113" s="2" t="n"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5885,27 +6565,33 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" s="2" t="n">
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" s="2" t="n">
         <v>44950</v>
       </c>
-      <c r="J114" s="2" t="n"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
+      <c r="K114" s="2" t="n"/>
+      <c r="L114" s="2" t="n"/>
       <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5930,31 +6616,37 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>7급</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" s="2" t="n">
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" s="2" t="n">
         <v>39565</v>
       </c>
-      <c r="J115" s="2" t="n"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr">
+      <c r="K115" s="2" t="n"/>
+      <c r="L115" s="2" t="n"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5979,31 +6671,37 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>6급</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" s="2" t="n">
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" s="2" t="n">
         <v>44030</v>
       </c>
-      <c r="J116" s="2" t="n"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr">
+      <c r="K116" s="2" t="n"/>
+      <c r="L116" s="2" t="n"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6028,27 +6726,33 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" s="2" t="n">
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" s="2" t="n">
         <v>44826</v>
       </c>
-      <c r="J117" s="2" t="n"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
+      <c r="K117" s="2" t="n"/>
+      <c r="L117" s="2" t="n"/>
       <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6073,31 +6777,39 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" s="2" t="n">
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" s="2" t="n">
         <v>39715</v>
       </c>
-      <c r="J118" s="2" t="n"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
+      <c r="K118" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="L118" s="2" t="n"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6122,31 +6834,37 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" s="2" t="n">
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" s="2" t="n">
         <v>43897</v>
       </c>
-      <c r="J119" s="2" t="n"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr">
+      <c r="K119" s="2" t="n"/>
+      <c r="L119" s="2" t="n"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6171,27 +6889,33 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" s="2" t="n">
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" s="2" t="n">
         <v>43396</v>
       </c>
-      <c r="J120" s="2" t="n"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
+      <c r="K120" s="2" t="n"/>
+      <c r="L120" s="2" t="n"/>
       <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6216,31 +6940,37 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
+          <t>5급</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" s="2" t="n">
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" s="2" t="n">
         <v>41593</v>
       </c>
-      <c r="J121" s="2" t="n"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr">
+      <c r="K121" s="2" t="n"/>
+      <c r="L121" s="2" t="n"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6265,31 +6995,37 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>6급</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t>무기계약직</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" s="2" t="n">
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" s="2" t="n">
         <v>45529</v>
       </c>
-      <c r="J122" s="2" t="n"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr">
+      <c r="K122" s="2" t="n"/>
+      <c r="L122" s="2" t="n"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6314,27 +7050,33 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
+          <t>7급</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t>기간제</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>사무</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>일근</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" s="2" t="n">
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" s="2" t="n">
         <v>40127</v>
       </c>
-      <c r="J123" s="2" t="n"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
+      <c r="K123" s="2" t="n"/>
+      <c r="L123" s="2" t="n"/>
       <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
